--- a/utils/monday_sprint_sprint_2024-43.xlsx
+++ b/utils/monday_sprint_sprint_2024-43.xlsx
@@ -153,7 +153,7 @@
     <t>09/05/2024</t>
   </si>
   <si>
-    <t>15/04/2026</t>
+    <t>10/04/2026</t>
   </si>
   <si>
     <t>Feito</t>
@@ -4144,7 +4144,7 @@
         <v>48</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -4170,7 +4170,7 @@
         <v>21</v>
       </c>
       <c r="Q12">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
@@ -4270,7 +4270,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>74</v>
@@ -4284,7 +4284,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>74</v>
@@ -4298,7 +4298,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>41</v>

--- a/utils/monday_sprint_sprint_2024-43.xlsx
+++ b/utils/monday_sprint_sprint_2024-43.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1075" uniqueCount="237">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>26610</t>
+    <t>6883632192</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,13 +87,13 @@
     <t>21/06/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>21/07/2024</t>
   </si>
   <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
+    <t>Não</t>
   </si>
   <si>
     <t>Semana 3</t>
@@ -102,7 +102,7 @@
     <t>Junho</t>
   </si>
   <si>
-    <t>26122</t>
+    <t>6794789928</t>
   </si>
   <si>
     <t>Melhorias sistema de investimentos</t>
@@ -114,7 +114,7 @@
     <t>Semana 1</t>
   </si>
   <si>
-    <t>26795</t>
+    <t>6973375682</t>
   </si>
   <si>
     <t>Divergência QlikSense - REFUGO</t>
@@ -126,13 +126,13 @@
     <t>Julho</t>
   </si>
   <si>
-    <t>25496</t>
+    <t>6884036333</t>
   </si>
   <si>
     <t>Melhorias app checklist</t>
   </si>
   <si>
-    <t>27468</t>
+    <t>7243710344</t>
   </si>
   <si>
     <t>Extração Realizado Benner</t>
@@ -141,28 +141,31 @@
     <t>16/08/2024</t>
   </si>
   <si>
+    <t>18/08/2024</t>
+  </si>
+  <si>
     <t>Agosto</t>
   </si>
   <si>
-    <t>26511</t>
+    <t>6883960765</t>
   </si>
   <si>
     <t>Melhoria QlikSense</t>
   </si>
   <si>
-    <t>26553</t>
+    <t>6883887327</t>
   </si>
   <si>
     <t>Dashboard QlickSense - Log &amp; Exp</t>
   </si>
   <si>
-    <t>26772</t>
+    <t>6973391660</t>
   </si>
   <si>
     <t>Criar um novo relatório</t>
   </si>
   <si>
-    <t>26853</t>
+    <t>7061076528</t>
   </si>
   <si>
     <t>Diferença - Faturamento x QSense</t>
@@ -201,16 +204,13 @@
     <t>Feito</t>
   </si>
   <si>
-    <t>Não</t>
-  </si>
-  <si>
     <t>Semana 2</t>
   </si>
   <si>
     <t>Maio</t>
   </si>
   <si>
-    <t>27220</t>
+    <t>7152306182</t>
   </si>
   <si>
     <t>Tabela Saldo Depósito</t>
@@ -219,13 +219,16 @@
     <t>02/08/2024</t>
   </si>
   <si>
-    <t>27140</t>
+    <t>04/08/2024</t>
+  </si>
+  <si>
+    <t>7152616352</t>
   </si>
   <si>
     <t>Qlik sense</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>5814001000</t>
   </si>
   <si>
     <t>Ordem de Coleta e Entrega - Mockup</t>
@@ -237,7 +240,7 @@
     <t>Janeiro</t>
   </si>
   <si>
-    <t>27354</t>
+    <t>7242642147</t>
   </si>
   <si>
     <t>Peso por área x Qlik Sense</t>
@@ -249,7 +252,10 @@
     <t>Gravar tempo padrão nas tabelas de tempo de ajustagem (IROG)</t>
   </si>
   <si>
-    <t>26505</t>
+    <t>29/08/2024</t>
+  </si>
+  <si>
+    <t>7251209239</t>
   </si>
   <si>
     <t>WMS - Adequação SPS</t>
@@ -258,16 +264,19 @@
     <t>19/08/2024</t>
   </si>
   <si>
-    <t>27361</t>
+    <t>7242586934</t>
   </si>
   <si>
     <t>Senha movimentação Bloqueio</t>
   </si>
   <si>
+    <t>27/08/2024</t>
+  </si>
+  <si>
     <t>Impedimento</t>
   </si>
   <si>
-    <t>27536</t>
+    <t>7276355120</t>
   </si>
   <si>
     <t>Liberação para Não Prrenchimento de Formulários Extras de ACVO</t>
@@ -276,18 +285,18 @@
     <t>22/08/2024</t>
   </si>
   <si>
+    <t>28/08/2024</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>27532</t>
+    <t>7327620740</t>
   </si>
   <si>
     <t>Planilha carga maquina usinagem</t>
   </si>
   <si>
-    <t>29/08/2024</t>
-  </si>
-  <si>
     <t>Semana 5</t>
   </si>
   <si>
@@ -300,6 +309,9 @@
     <t>25310</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Sistema de Controle de Orçamento de Entregas de Venda</t>
   </si>
   <si>
@@ -315,25 +327,28 @@
     <t>28/03/2024</t>
   </si>
   <si>
+    <t>14/08/2024</t>
+  </si>
+  <si>
     <t>Em Análise</t>
   </si>
   <si>
     <t>Março</t>
   </si>
   <si>
-    <t>26926</t>
+    <t>7060958949</t>
   </si>
   <si>
     <t>SPA - Cálculo de IROG via QlikSense</t>
   </si>
   <si>
-    <t>27357</t>
+    <t>7242634322</t>
   </si>
   <si>
     <t>Cenário Valorização</t>
   </si>
   <si>
-    <t>24256</t>
+    <t>5990640199</t>
   </si>
   <si>
     <t>Sistema GIQ</t>
@@ -345,40 +360,49 @@
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>27333</t>
+    <t>7242667255</t>
   </si>
   <si>
     <t>Sistema de Cadastro de modelos</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>7239444613</t>
   </si>
   <si>
     <t>Mecanismo de referencia programadas</t>
   </si>
   <si>
-    <t>27421</t>
+    <t>25/08/2024</t>
+  </si>
+  <si>
+    <t>7242473405</t>
   </si>
   <si>
     <t>Tela de conferencia</t>
   </si>
   <si>
+    <t>7251374644</t>
+  </si>
+  <si>
     <t>Projeto</t>
   </si>
   <si>
     <t>AJUSTES CONDIÇÃO DE PAGAMENTO OFERTA / CPC</t>
   </si>
   <si>
+    <t>02/09/2024</t>
+  </si>
+  <si>
     <t>Implantação</t>
   </si>
   <si>
-    <t>27121</t>
+    <t>7250397509</t>
   </si>
   <si>
     <t>SIC WEB Aprovação de gestores da area</t>
   </si>
   <si>
-    <t>27375</t>
+    <t>7242551622</t>
   </si>
   <si>
     <t>Projeto de melhoria - Divergência apontamentos solda</t>
@@ -387,37 +411,55 @@
     <t>Baixa</t>
   </si>
   <si>
-    <t>27476</t>
+    <t>7253613200</t>
   </si>
   <si>
     <t>Criar relatório (planilha) no portal de notas de entrada para a consulta dos CTEs recebidos x notas lançadas no sistema sem o frete</t>
   </si>
   <si>
+    <t>7253625320</t>
+  </si>
+  <si>
     <t>Criar tela para lançar o frete e vincular quando a nota já estiver lançada</t>
   </si>
   <si>
     <t>Fazendo</t>
   </si>
   <si>
+    <t>7259200606</t>
+  </si>
+  <si>
     <t>Preparar o ambiente e tela de login</t>
   </si>
   <si>
     <t>20/08/2024</t>
   </si>
   <si>
+    <t>7259202005</t>
+  </si>
+  <si>
     <t>Cadastro de indicadores pela GIQ mês a mês</t>
   </si>
   <si>
+    <t>7259202771</t>
+  </si>
+  <si>
     <t>Tela (para manutenção pela GIQ) de cadastro de área x usuários responsáveis pelos indicadores</t>
   </si>
   <si>
+    <t>7259205517</t>
+  </si>
+  <si>
     <t>Tela para o usuário responsável pela área informar o valor/índice alcançado no mês</t>
   </si>
   <si>
+    <t>7259206515</t>
+  </si>
+  <si>
     <t>Cadastro e manutenção do plano de ação</t>
   </si>
   <si>
-    <t>26829</t>
+    <t>7113162597</t>
   </si>
   <si>
     <t>Segregação custeiro - Fundição - 5.1.2.01.111-Refratários ácidos / 5.1.2.01.117-Luvas exotérmicas</t>
@@ -426,67 +468,91 @@
     <t>29/07/2024</t>
   </si>
   <si>
+    <t>03/09/2024</t>
+  </si>
+  <si>
+    <t>7113172440</t>
+  </si>
+  <si>
     <t>Segregação custeiro - Fundição - 5.1.2.01.103-Resinas / 5.1.2.01.110 - Aglomerantes</t>
   </si>
   <si>
+    <t>7113176525</t>
+  </si>
+  <si>
     <t>Segregação custeiro - Fundição - MOD/MOI/GGV/GGF/Depreciação/Apoio Industrial</t>
   </si>
   <si>
-    <t>26830</t>
+    <t>7113190665</t>
   </si>
   <si>
     <t>Segregação custeiro - Acabamento - Tratamento térmico</t>
   </si>
   <si>
+    <t>7113193619</t>
+  </si>
+  <si>
     <t>Segregação custeiro - Acabamento - Rebarbação</t>
   </si>
   <si>
+    <t>7113196637</t>
+  </si>
+  <si>
     <t>Segregação custeiro - Acabamento - Apoio industrial</t>
   </si>
   <si>
-    <t>27328</t>
+    <t>7242691051</t>
   </si>
   <si>
     <t>Melhoria sistema de modelo</t>
   </si>
   <si>
-    <t>25813</t>
+    <t>6619728872</t>
   </si>
   <si>
     <t>WMS - Inventário</t>
   </si>
   <si>
-    <t>27353</t>
+    <t>7242650173</t>
   </si>
   <si>
     <t>Acerto de valor de MOEDA - BENNER</t>
   </si>
   <si>
-    <t>27013</t>
+    <t>7239431196</t>
   </si>
   <si>
     <t>Será utilizado materiais da tabela de materiais, para isso será necessário criar campos extras para a tela</t>
   </si>
   <si>
-    <t>27287</t>
+    <t>7242784092</t>
   </si>
   <si>
     <t>Concilia Relatório Planilha Custeio - Sistemas de Corridas - Análise</t>
   </si>
   <si>
+    <t>26/08/2024</t>
+  </si>
+  <si>
+    <t>7239433887</t>
+  </si>
+  <si>
     <t>Tela com o saldo dos materiais e para a requisição dos materiais</t>
   </si>
   <si>
+    <t>7239435939</t>
+  </si>
+  <si>
     <t>Relatórios de consumo</t>
   </si>
   <si>
-    <t>27115</t>
+    <t>7242815340</t>
   </si>
   <si>
     <t>ALTERAÇÃO DO RELATÓRIO DE ANÁLISE CRÍTICA ITENS COMERCIAIS</t>
   </si>
   <si>
-    <t>27451</t>
+    <t>7242448406</t>
   </si>
   <si>
     <t>Análise</t>
@@ -495,55 +561,58 @@
     <t>PENDÊNCIA ESPECIAL 2 SETORES SIMULTÂNEOS</t>
   </si>
   <si>
-    <t>27443</t>
+    <t>7242457797</t>
   </si>
   <si>
     <t>Engate rápido 11157530</t>
   </si>
   <si>
-    <t>27452</t>
+    <t>7242402757</t>
   </si>
   <si>
     <t>Controle de Procedimentos x Pré-produtivo</t>
   </si>
   <si>
-    <t>27416</t>
+    <t>7242484973</t>
   </si>
   <si>
     <t>ALTERAÇÃO DA TELA DE DADOS DO CONJUNTO</t>
   </si>
   <si>
-    <t>27396</t>
+    <t>7242516491</t>
   </si>
   <si>
     <t>Alteração lançamento fiscal ativo imobilizado</t>
   </si>
   <si>
-    <t>27477</t>
+    <t>7250254157</t>
   </si>
   <si>
     <t>DOCUMENTAÇÃO DE CLIENTE CADASTRADA NO CPP</t>
   </si>
   <si>
-    <t>27459</t>
+    <t>7251178964</t>
   </si>
   <si>
     <t>WMS - Contentor</t>
   </si>
   <si>
-    <t>27403</t>
+    <t>21/08/2024</t>
+  </si>
+  <si>
+    <t>7242503908</t>
   </si>
   <si>
     <t>Instalação de botão voltar na tela de parcelas</t>
   </si>
   <si>
-    <t>27461</t>
+    <t>7251142667</t>
   </si>
   <si>
     <t>WMS - Incluir e Excluir contentor</t>
   </si>
   <si>
-    <t>27228</t>
+    <t>7287131844</t>
   </si>
   <si>
     <t>Correção</t>
@@ -558,19 +627,19 @@
     <t>23/08/2024</t>
   </si>
   <si>
-    <t>25205</t>
+    <t>6973877336</t>
   </si>
   <si>
     <t>PDI Eletrônico II</t>
   </si>
   <si>
-    <t>27179</t>
+    <t>7152579708</t>
   </si>
   <si>
     <t>PDI Eletrônico (Níveis de Disposição)</t>
   </si>
   <si>
-    <t>25636</t>
+    <t>7162025807</t>
   </si>
   <si>
     <t>Validar o botão de importar</t>
@@ -585,7 +654,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-43</t>
+    <t>Jan/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1356,7 +1425,7 @@
         <v>41</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1368,12 +1437,12 @@
         <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1385,10 +1454,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1420,7 +1489,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1432,10 +1501,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1467,7 +1536,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1479,10 +1548,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1514,7 +1583,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1526,10 +1595,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1541,7 +1610,7 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>24</v>
@@ -1561,43 +1630,43 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>63</v>
@@ -1638,7 +1707,7 @@
         <v>67</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1650,12 +1719,12 @@
         <v>32</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1667,10 +1736,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1685,7 +1754,7 @@
         <v>67</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1697,12 +1766,12 @@
         <v>32</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1714,10 +1783,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1729,10 +1798,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1744,12 +1813,12 @@
         <v>63</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1761,10 +1830,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1779,7 +1848,7 @@
         <v>41</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1791,12 +1860,12 @@
         <v>27</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1808,10 +1877,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1826,24 +1895,24 @@
         <v>41</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1855,42 +1924,42 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L17" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1902,10 +1971,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1920,10 +1989,10 @@
         <v>41</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>26</v>
@@ -1932,12 +2001,12 @@
         <v>27</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1949,10 +2018,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1964,27 +2033,27 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1996,10 +2065,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -2011,27 +2080,27 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L20" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2043,10 +2112,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -2058,74 +2127,74 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="K21" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L21" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2137,10 +2206,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2152,7 +2221,7 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>24</v>
@@ -2172,7 +2241,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2184,10 +2253,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2202,7 +2271,7 @@
         <v>41</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -2214,12 +2283,12 @@
         <v>27</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2231,10 +2300,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2246,27 +2315,27 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>32</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2278,10 +2347,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2296,24 +2365,24 @@
         <v>41</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2325,10 +2394,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2343,24 +2412,24 @@
         <v>41</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2372,10 +2441,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2390,7 +2459,7 @@
         <v>41</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2402,27 +2471,27 @@
         <v>27</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2434,27 +2503,27 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2466,10 +2535,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2481,42 +2550,42 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2531,7 +2600,7 @@
         <v>41</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2543,42 +2612,42 @@
         <v>27</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2590,12 +2659,12 @@
         <v>27</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2607,10 +2676,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2622,27 +2691,27 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2654,10 +2723,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2669,13 +2738,13 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>26</v>
@@ -2684,12 +2753,12 @@
         <v>27</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2701,10 +2770,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2716,27 +2785,27 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2748,10 +2817,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2763,27 +2832,27 @@
         <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2795,10 +2864,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2810,27 +2879,27 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2842,10 +2911,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2857,27 +2926,27 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2889,10 +2958,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2904,27 +2973,27 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2936,10 +3005,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2951,19 +3020,19 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>36</v>
@@ -2971,7 +3040,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2983,10 +3052,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2998,19 +3067,19 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>36</v>
@@ -3018,7 +3087,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -3030,10 +3099,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -3045,19 +3114,19 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>36</v>
@@ -3065,7 +3134,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3077,10 +3146,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3092,19 +3161,19 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L43" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K43" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="M43" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>36</v>
@@ -3112,7 +3181,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>139</v>
+        <v>158</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3124,10 +3193,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3139,19 +3208,19 @@
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L44" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K44" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="M44" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>36</v>
@@ -3159,7 +3228,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3171,10 +3240,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -3186,19 +3255,19 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L45" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="M45" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>36</v>
@@ -3206,7 +3275,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3218,10 +3287,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3236,24 +3305,24 @@
         <v>41</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3265,10 +3334,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3280,16 +3349,16 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>63</v>
@@ -3300,7 +3369,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3312,10 +3381,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3330,24 +3399,24 @@
         <v>41</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3359,10 +3428,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3377,24 +3446,24 @@
         <v>41</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3406,10 +3475,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3424,24 +3493,24 @@
         <v>41</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3453,10 +3522,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3471,24 +3540,24 @@
         <v>41</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3500,10 +3569,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3518,24 +3587,24 @@
         <v>41</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3547,10 +3616,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3565,39 +3634,39 @@
         <v>41</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
@@ -3612,24 +3681,24 @@
         <v>41</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3641,10 +3710,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3659,24 +3728,24 @@
         <v>41</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3688,10 +3757,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3706,24 +3775,24 @@
         <v>41</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3735,10 +3804,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -3753,24 +3822,24 @@
         <v>41</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -3782,10 +3851,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
@@ -3800,24 +3869,24 @@
         <v>41</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
@@ -3829,10 +3898,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -3844,27 +3913,27 @@
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -3876,10 +3945,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -3891,27 +3960,27 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
@@ -3923,10 +3992,10 @@
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
@@ -3941,24 +4010,24 @@
         <v>41</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -3970,10 +4039,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
@@ -3985,45 +4054,45 @@
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>21</v>
@@ -4032,27 +4101,27 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4064,13 +4133,13 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>21</v>
@@ -4082,13 +4151,13 @@
         <v>35</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>32</v>
@@ -4099,7 +4168,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
@@ -4111,10 +4180,10 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>20</v>
@@ -4129,24 +4198,24 @@
         <v>67</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>32</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
@@ -4158,10 +4227,10 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
@@ -4173,22 +4242,22 @@
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>139</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>32</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -4204,23 +4273,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="D2" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="E2" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4228,16 +4297,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4248,20 +4317,20 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>700</v>
+        <v>36.66</v>
       </c>
       <c r="J5" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K22">
         <v>40</v>
@@ -4269,7 +4338,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -4277,7 +4346,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4308,12 +4377,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="B2">
         <v>65</v>
@@ -4327,35 +4396,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>700</v>
+        <v>36.66</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -4363,7 +4432,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -4372,19 +4441,19 @@
         <v>61</v>
       </c>
       <c r="G10" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N10">
         <v>40</v>
@@ -4398,28 +4467,28 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E11">
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="K11">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="M11" t="s">
         <v>25</v>
@@ -4431,12 +4500,18 @@
         <v>63</v>
       </c>
       <c r="Q11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4448,13 +4523,13 @@
         <v>62</v>
       </c>
       <c r="J12" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="K12">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -4463,58 +4538,58 @@
         <v>27</v>
       </c>
       <c r="Q12">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H13">
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="N13">
         <v>4</v>
       </c>
       <c r="P13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="Q13">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="N14">
         <v>1</v>
       </c>
       <c r="P14" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="Q14">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4522,7 +4597,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4530,7 +4605,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -4538,10 +4613,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -4549,7 +4624,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -4557,142 +4632,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>685</v>
+        <v>877</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>89</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>877</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
